--- a/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>VALENTE</t>
-  </si>
-  <si>
-    <t>PULIDO</t>
-  </si>
-  <si>
-    <t>JUAN EMANUEL</t>
   </si>
 </sst>
 </file>
@@ -535,7 +526,7 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -544,10 +535,10 @@
         <v>3</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>91.89</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
         <v>7.7</v>
@@ -655,16 +646,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.22</v>
+      </c>
+      <c r="H2">
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -678,16 +672,19 @@
         <v>23</v>
       </c>
       <c r="D3">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -698,19 +695,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>88.89</v>
+      </c>
+      <c r="H4">
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -724,16 +724,19 @@
         <v>26</v>
       </c>
       <c r="D5">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>92.31</v>
+      </c>
+      <c r="H5">
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -747,16 +750,19 @@
         <v>30</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>30</v>
       </c>
-      <c r="E6">
-        <v>30</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -812,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>94.44</v>
+        <v>97.22</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -838,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3">
-        <v>82.61</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -858,22 +864,22 @@
         <v>11</v>
       </c>
       <c r="C4">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>91.89</v>
+        <v>88.89</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -925,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -965,29 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920401</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
@@ -844,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>95.65000000000001</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -870,13 +870,13 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>88.89</v>
+        <v>91.67</v>
       </c>
       <c r="H4">
         <v>7.8</v>
@@ -896,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5">
-        <v>92.31</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="H5">
         <v>9.199999999999999</v>
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
@@ -827,7 +827,7 @@
         <v>97.22</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,7 +879,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,7 +905,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
+++ b/docentes/Martínez Castillo Columba - Estadisticos 20231.xlsx
@@ -827,7 +827,7 @@
         <v>97.22</v>
       </c>
       <c r="H2">
-        <v>9.9</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +853,7 @@
         <v>100</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -879,7 +879,7 @@
         <v>91.67</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -905,7 +905,7 @@
         <v>96.15000000000001</v>
       </c>
       <c r="H5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -931,7 +931,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
